--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_03_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_03_20_Cau.xlsx
@@ -727,7 +727,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Pre-render redaction, Regex và entity recognition.</t>
+          <t>Nguyên tắc che dữ liệu nhạy cảm (PII redaction): Việc làm sạch dữ liệu phải được thực hiện tại ranh giới ứng dụng trước khi phát đi (redact-before-emission), ngăn chặn PII lọt vào bất kỳ bộ đệm trace hay log nào.</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Execution context, Context binding.</t>
+          <t>Trong các ứng dụng bất đồng bộ chạy nhiều coroutines, dữ liệu ngữ cảnh của người dùng phải được cô lập độc lập theo từng task (sử dụng `contextvars.ContextVar`) để tránh tình trạng race-condition gây lẫn lộn thông tin tenant.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>99100</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
@@ -1143,7 +1147,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách error khỏi normal trước khi áp sampling rate.</t>
+          <t>Tổng số event giữ lại: Error events (100% của 1% * 1.000.000 = 10.000) + Normal events (9% của 99% * 1.000.000 = 0,09 * 990.000 = 89.100). Tổng cộng: 10.000 + 89.100 = 99.100 event.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1315,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Trace identity, Root/child span.</t>
+          <t>Trong kiến trúc microservices và hàng đợi async, trace context bắt buộc phải được truyền (propagate) và liên kết xuyên suốt qua các message queue để bảo đảm quan hệ nhân quả (causality) giữa các span.</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1397,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Root invocation, Model generation span.</t>
+          <t>Thiết kế span hữu ích cho agent loop: Nên phân tách span theo từng tác vụ thao tác cụ thể (plan, retrieve, model call, tool execution, retry) thay vì gom toàn bộ vào một span duy nhất hoặc chia vụn theo từng token.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_03_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_03_20_Cau.xlsx
@@ -676,10 +676,31 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Purpose limitation, Field allowlist.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Purpose limitation, Field allowlist.</t>
+- 1.0đ: Xác định đúng mục COLLECT cho các trường hạ tầng cốt lõi (operation name, trace_id, payload size).
+- 1.0đ: Thiết kế cơ chế TRANSFORM bảo vệ dữ liệu (hashing có muối cho customer_id, masking tham số).
+- 1.0đ: Thiết kế cơ chế SUMMARIZE cho arguments (lưu khóa tham số, schema validity thay vì raw value).
+- 1.0đ: Chỉ rõ các trường OMIT bắt buộc loại bỏ hoàn toàn (raw sensitive values, secrets, tokens).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lập kế hoạch xử lý Telemetry Tool-Call theo 4 cấp độ: Collect, Transform, Summarize, và Omit:
+1. **COLLECT (Thu thập nguyên trạng có kiểm soát)**:
+- `operation_name`: Tên công cụ/hàm nghiệp vụ được gọi (e.g., `lookup_customer_balance`). Bắt buộc thu thập để định tuyến trace.
+- `timestamp`, `trace_id`, `span_id`: Định danh ngữ cảnh phân tán. Thu thập đầy đủ.
+- `payload_size_bytes`: Kích thước payload tính bằng byte. Thu thập để phân tích băng thông.
+2. **TRANSFORM (Chuyển đổi bảo vệ quyền riêng tư)**:
+- `customer_id`: Chuyển đổi bằng phương pháp hàm băm mật mã một chiều kèm muối (Salted SHA-256 Hashing) thành `customer_hash_id`. Cho phép nhóm các thao tác của cùng một khách hàng mà không để lộ danh tính thực.
+- Các tham số đầu vào nhạy cảm (e.g., số thẻ, email): Áp dụng masking quy tắc (ví dụ: `email@***.com`, `****-****-****-1234`).
+3. **SUMMARIZE (Tóm tắt cấu trúc thay vì lưu chi tiết)**:
+- `full_arguments`: Không lưu toàn bộ giá trị cụ thể của arguments; chuyển đổi thành metadata cấu trúc:
+  + `arg_keys`: Danh sách các khóa tham số được truyền vào (e.g., `['account_id', 'date_range', 'currency']`).
+  + `arg_count`: Số lượng tham số.
+  + `schema_valid`: Cờ boolean xác nhận tham số có đúng JSON schema hay không.
+4. **OMIT (Loại bỏ hoàn toàn)**:
+- `raw_argument_values` chứa dữ liệu văn bản tự do hoặc PII không cần thiết cho mục đích SRE.
+- `internal_auth_tokens` / `api_credentials`: Tuyệt đối xóa bỏ khỏi mọi trace payload.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Dữ liệu Giám sát (Telemetry Payload Minimization): Một sự kiện trace không bao giờ được trở thành kênh rò rỉ dữ liệu nhạy cảm. Áp dụng ma trận 4 bước Collect-Transform-Summarize-Omit giúp phân định rõ ràng mục đích sử dụng của từng thuộc tính: giữ lại các metadata cần thiết cho SRE (tên hàm, kích thước, cấu trúc tham số), băm hoặc che các trường định danh, và loại bỏ triệt để các dữ liệu tuyệt mật.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST Special Publication 800-53: Privacy and Security Controls &amp; OpenTelemetry Collector Sensitive Data Processing</t>
         </is>
       </c>
     </row>
@@ -758,10 +779,27 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Pre-render redaction, Regex và entity recognition.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Pre-render redaction, Regex và entity recognition.</t>
+- 1.0đ: Thiết kế cơ chế duyệt đệ quy (recursive traversal) xử lý triệt để cấu trúc nested và list.
+- 1.0đ: Xây dựng bộ lọc Regex/NER khử khuẩn free-text error message cho email và số điện thoại.
+- 1.0đ: Thiết lập whitelist bảo tồn an toàn cho correlation IDs và trace metadata.
+- 1.0đ: Xây dựng kịch bản kiểm thử phủ định (Negative Verification) kiểm tra cả zero leakage và không over-redact.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Bộ lọc Che chắn Dữ liệu Nhạy cảm (PII Scrubber Pipeline):
+- **Bộ duyệt cấu trúc đệ quy (Recursive Object Traversal)**: Scrubber duyệt qua toàn bộ cấu trúc dữ liệu nested (Dictionaries, Lists, Primitives):
+  + Đối với danh sách (Lists): Duyệt từng phần tử; kiểm tra pattern đối với chuỗi điện thoại/email dạng danh sách số điện thoại `[phone1, phone2]`.
+  + Đối với khóa đã biết (Known Keys): Nếu key nằm trong danh bạ nhạy cảm (e.g., `email`, `phone`, `ssn`, `password`), tự động ghi đè giá trị bằng `[REDACTED_EMAIL]`, `[REDACTED_PHONE]`.
+- **Regex &amp; NLP Scrubber cho Free-text Error**:
+  + Áp dụng Regex chuẩn RFC 5322 cho Email và E.164 cho Số điện thoại để quét toàn bộ chuỗi văn bản tự do trong trường error message.
+  + Tích hợp mô hình Named Entity Recognition (NER) nhẹ để nhận diện tên người hoặc địa chỉ nằm trong stack trace.
+- **Bảo tồn trường an toàn (Preservation Whitelist)**:
+  + Khóa `correlation_id`, `trace_id`, `span_id` được đưa vào whitelist miễn trừ khử khuẩn để giữ nguyên vẹn chuỗi liên kết chẩn đoán.
+2. Thiết kế Kiểm thử Xác minh Phủ định (Negative Verification Test Suite):
+- **Test Case 1 (PII Leakage Rejection)**: Bơm payload giả lập chứa 50 biến thể email (cả chữ hoa, chữ thường, unicode), số điện thoại quốc tế nằm lồng ghép 4 tầng object/array và trong chuỗi error stack trace. Đo lường tỷ lệ rò rỉ: bắt buộc **100% PII bị che phủ**, không có bất kỳ ký tự nào lọt qua.
+- **Test Case 2 (Over-redaction &amp; Identity Integrity)**: Xác minh rằng `correlation_id` (ví dụ: `corr-uuid-1234-abcd`) KHÔNG bị scrubber nhầm lẫn là thông tin nhạy cảm và vẫn giữ nguyên giá trị ban đầu để đảm bảo năng lực truy vết.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Khử khuẩn Dữ liệu trước khi Phát thải (PII Redaction before Emission): Một khi dữ liệu telemetry đã bắn ra khỏi ứng dụng đến các nền tảng tập trung (Datadog, Loki, S3), việc thu hồi hoặc xóa bỏ là cực kỳ tốn kém và phức tạp về mặt tuân thủ pháp lý. Do đó, scrubber phải chạy ngay tại in-memory SDK trước khi phát thải ra network. Đồng thời, quy trình Negative Verification bắt buộc phải kiểm tra cả hai chiều: không để lọt PII (zero leakage) và không che nhầm các mã định danh kỹ thuật an toàn (zero false positives trên correlation IDs).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Automated Threat Handbook: Sensitive Data Exposure &amp; Microsoft Presidio Data Protection Documentation</t>
         </is>
       </c>
     </row>
@@ -892,10 +930,20 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra DEBUG, INFO.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra DEBUG, INFO.</t>
+- 1.0đ: Thiết kế cơ chế nâng log level động khu biệt chỉ riêng cho tenant mục tiêu (tenant-scoped dynamic logging).
+- 1.0đ: Thiết lập cơ chế tự hủy sau 30 phút (TTL / auto-revert timer) ngăn chặn rủi ro rò rỉ log kéo dài.
+- 1.0đ: Đảm bảo nguyên tắc khử khuẩn PII vẫn duy trì hiệu lực 100% ngay cả khi chạy mức DEBUG.
+- 1.0đ: Thiết lập nhật ký kiểm toán (audit log) ghi lại người kích hoạt, lý do sự cố và thời gian hiệu lực.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Nâng cấp Mức độ Chẩn đoán Tạm thời (Temporary Diagnostic Escalation):
+1. **Phạm vi Khu biệt (Scoped Escalation)**: Không nâng log level toàn hệ thống. Áp dụng Dynamic Log Level chỉ riêng cho `tenant_id == 'tenant_target'` thông qua cấu hình runtime động (etcd/Consul hoặc OpenTelemetry collector filter) từ mức `INFO` lên `DEBUG`.
+2. **Cơ chế Hạn chế Thời gian Tự hủy (Time-to-Live / Auto-revert)**: Đặt TTL nghiêm ngặt đúng 30 phút bằng bộ đếm giờ tự động (expiration token hoặc cron job). Sau 30 phút, hệ thống tự động hoàn nguyên về log level `INFO` mà không cần can thiệp thủ công, loại bỏ rủi ro quên tắt làm tràn dung lượng lưu trữ.
+3. **Bảo vệ PII Bắt buộc (Non-negotiable PII Redaction)**: Dù ở mức `DEBUG`, toàn bộ payload vẫn phải đi qua in-memory PII scrubber (khử khuẩn email, số điện thoại, số thẻ) trước khi ghi vào log stream. 'Tăng chi tiết' chỉ áp dụng cho cấu trúc tham số (argument keys, status codes, query execution plans, sub-step latency), tuyệt đối không mở khóa dữ liệu nhạy cảm của người dùng.
+4. **Audit Trail**: Ghi log kiểm toán thao tác quản trị: ai là người yêu cầu nâng cấp debug, lý do sự cố (incident ticket ID), thời điểm bắt đầu và kết thúc.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Vận hành Sự cố Bảo đảm Quyền riêng tư (Privacy-preserving Diagnostic Escalation): Khi xảy ra sự cố nghiêm trọng, kỹ sư thường có xu hướng bật mức DEBUG toàn cục, dẫn đến hai thảm họa: rò rỉ dữ liệu khách hàng (PII leakage) và bùng nổ chi phí lưu trữ/tắc nghẽn mạng do bão log. Một cơ chế chuẩn mực phải bảo đảm tính khu biệt theo tenant, có cơ chế tự hủy (TTL 30 phút), duy trì khử khuẩn PII bất di bất dịch, và lưu vết kiểm toán đầy đủ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Addressing Cascading Failures &amp; 12-Factor App: Logs (https://12factor.net/logs)</t>
         </is>
       </c>
     </row>
@@ -978,10 +1026,20 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Generate/validate ở boundary, Bind context sớm.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Generate/validate ở boundary, Bind context sớm.</t>
+- 1.0đ: Đặc tả khâu CREATE chuẩn xác tại gateway (UUID/W3C traceparent).
+- 1.0đ: Đặc tả khâu PROPAGATE sử dụng cơ chế bất đồng bộ an toàn (ContextVar/AsyncLocalStorage) ngăn chặn nhiễm chéo.
+- 1.0đ: Đặc tả khâu EXPOSE trả về header an toàn cho client đối soát không lộ bí mật nội bộ.
+- 1.0đ: Đặc tả khâu CLEAR trong khối finally để dọn sạch ngữ cảnh, tránh memory leak và context reuse bug.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Vòng đời Correlation ID (Create -&gt; Propagate -&gt; Expose -&gt; Clear) cho các yêu cầu bất đồng bộ đan xen:
+1. **CREATE (Khởi tạo)**: Khi request A và B đi vào Ingress Gateway, nếu chưa có header `X-Correlation-ID` (hoặc W3C `traceparent`), gateway sinh một UUID ngẫu nhiên duy nhất (ví dụ: `corr-reqA-xxxx` và `corr-reqB-yyyy`).
+2. **PROPAGATE (Lan truyền ngữ cảnh)**: Sử dụng cấu trúc lưu trữ ngữ cảnh bất đồng bộ an toàn (như Python `contextvars.ContextVar` hoặc Node.js `AsyncLocalStorage`). Mỗi khi gọi downstream service hoặc đẩy task vào hàng đợi (RabbitMQ/Kafka), correlation ID được tiêm (inject) vào HTTP headers (`X-Correlation-ID`) hoặc message metadata attributes. Vì A và B chạy xen kẽ trên cùng event loop/thread pool, việc dùng ContextVar bảo đảm ngữ cảnh của A không bị ghi đè sang B.
+3. **EXPOSE (Phơi bày an toàn)**: Trả correlation ID trong HTTP response header an toàn (`X-Correlation-ID`) về cho client để đối soát khiếu nại. Tuyệt đối không đính kèm thông tin nội bộ (như IP server, container ID, database credentials) trong header này.
+4. **CLEAR (Thu dọn giải phóng)**: Khi request hoàn tất (trong khối `finally`), thực hiện reset/clear context token tương ứng để ngăn chặn memory leak hoặc rò rỉ ngữ cảnh sang request tiếp theo tái sử dụng worker thread.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản lý Vòng đời Correlation ID: Trong các hệ thống microservices và xử lý bất đồng bộ (async event loops), nhiều request được xử lý đan xen (interleaved). Nếu sử dụng biến toàn cục hoặc ThreadLocal không an toàn, correlation ID của request này sẽ bị gán nhầm cho request khác, phá hủy hoàn toàn khả năng gỡ lỗi. Thiết kế chuẩn W3C Trace Context và ContextVar đảm bảo tính cô lập tuyệt đối từ khi sinh ra, truyền qua mạng, trả cho client và thu dọn khi kết thúc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C Trace Context Specification (https://www.w3.org/TR/trace-context/) &amp; OpenTelemetry Context Propagation Guide</t>
         </is>
       </c>
     </row>
@@ -1108,10 +1166,24 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Execution context, Context binding.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Execution context, Context binding.</t>
+- 1.0đ: Thiết kế cơ chế cô lập ngữ cảnh async bằng ContextVar và sao chép snapshot bất biến (immutable context copy).
+- 1.0đ: Phân định rành mạch ngữ cảnh giữa HTTP request cha và background job độc lập (parent correlation tracking).
+- 1.0đ: Thiết kế test case kiểm tra đan xen đồng thời (concurrency interleaving) bảo đảm 0% context bleed.
+- 1.0đ: Thiết kế test case kiểm tra vòng đời background task xác nhận không bị rò rỉ ngữ cảnh sang request kế tiếp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Cô lập Ngữ cảnh Bất đồng bộ (Async Log Context Isolation):
+- **Sử dụng ContextVar với Shallow Copy / Token Snapshot**: Trong môi trường async (như Python `asyncio`), sử dụng `contextvars.ContextVar` để lưu trữ log metadata (`request_id`, `tenant_id`).
+- **Cắt đứt liên kết khi Spawn Background Job**: Khi một request sinh ra background task sau khi đã trả response (e.g., `asyncio.create_task()` hoặc Celery/Kafka worker):
+  + Không truyền trực tiếp context con trỏ của thread cha sang job chạy ngầm.
+  + Khởi tạo một Execution Context độc lập cho background task, gán `job_id` mới riêng biệt, và chỉ sao chép một bản snapshot bất biến (immutable snapshot) các trường cha cần thiết (`parent_request_id = reqA`).
+  + Đảm bảo khi background job ghi log, nó phát thải `context_type: background_worker`, không làm ảnh hưởng đến ngữ cảnh của các HTTP request khác.
+2. Thiết kế Kiểm thử Đan xen &amp; Tác vụ Nền (Test Interleaving &amp; Background Isolation Suite):
+- **Test Case 1 (High-concurrency Async Interleaving)**: Tạo 1.000 coroutines đồng thời với các correlation IDs khác nhau (`req_001` đến `req_1000`). Mỗi coroutine thực hiện nhiều điểm dừng `await asyncio.sleep(0.01)` đan xen. Xác minh rằng 100% dòng log phát sinh trong mỗi coroutine có correlation ID khớp chính xác với ID được cấp phát ban đầu, tỷ lệ lẫn lộn (context bleed) là **0%**.
+- **Test Case 2 (Background Task Context Decoupling)**: Khởi tạo Request A, spawn background job J, kết thúc Request A và kích hoạt Request B ngay trên cùng worker. Xác minh rằng các log của Job J không bao giờ chứa thông tin của Request B, và log của Request B không kế thừa sót lại bất kỳ dữ liệu nào của Job J.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng Context Bleeding (chảy máu ngữ cảnh log) là lỗi phổ biến trong các ứng dụng async: do worker thread hoặc event loop được tái sử dụng liên tục, nếu không cô lập ngữ cảnh thông qua snapshot và dọn dẹp biến ngữ cảnh (context reset), các tác vụ chạy ngầm (background jobs) sẽ ghi nhận sai correlation ID của các request người dùng đến sau. Điều này gây thảm họa bảo mật khi thông tin của tenant này bị gắn nhầm vào log của tenant khác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Python contextvars Documentation (PEP 567) &amp; OpenTelemetry Python Context Isolation Guidelines</t>
         </is>
       </c>
     </row>
@@ -1178,10 +1250,27 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Giữ log theo severity, Sample routine event.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Giữ log theo severity, Sample routine event.</t>
+- 1.0đ: Thiết kế thang ưu tiên phân loại rõ ràng (Error &gt; High Latency &gt; High Cost &gt; Random Baseline).
+- 1.0đ: Cơ chế gắn nhãn nguyên nhân duy nhất (single sample_reason) kết hợp đa cờ thuộc tính (multi-tags).
+- 1.0đ: Triệt tiêu hoàn toàn hiện tượng tính trùng (zero double-counting) nhờ kiến trúc tail-sampling có bộ đệm.
+- 1.0đ: Giữ trọn vẹn khả năng chẩn đoán đa chiều khi truy vấn sự cố chồng lấn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Lấy mẫu Telemetry Định hướng Kết quả (Outcome-aware Telemetry Sampling) không trùng lặp (Zero Double-counting):
+1. **Quy tắc Phân loại Ưu tiên (Hierarchical Outcome Rules)**:
+Khi một sự kiện đồng thời thỏa mãn nhiều điều kiện bất thường (vừa bị lỗi ERROR, vừa bị CHẬM &gt; 5s, vừa có CHI PHÍ CAO &gt; $0.1), hệ thống áp dụng thang ưu tiên duy nhất (Disjoint Priority Bucket) để gán nhãn mẫu mà không nhân bản dữ liệu:
+- **Bậc 1: Error Events (`status == 'ERROR'`)** -&gt; Lấy mẫu 100% (Tail Sampling). Gán nhãn `sample_reason = 'ERROR'`.
+- **Bậc 2: High Latency Events (`latency &gt; P99 threshold` và không phải Error)** -&gt; Lấy mẫu 100%. Gán nhãn `sample_reason = 'HIGH_LATENCY'`.
+- **Bậc 3: High Cost Events (`token_cost &gt; threshold` và không rơi vào Bậc 1, 2)** -&gt; Lấy mẫu 100%. Gán nhãn `sample_reason = 'HIGH_COST'`.
+- **Bậc 4: Standard Success Traffic** -&gt; Lấy mẫu ngẫu nhiên xác suất thấp (ví dụ: 1-5%). Gán nhãn `sample_reason = 'BASELINE_RANDOM'`.
+2. **Cơ chế Triệt tiêu Trùng lặp (Deduplication &amp; Single-Emission Contract)**:
+- Sử dụng bộ đệm bộ nhớ tại Collector (Tail-sampling Processor): Collector gom toàn bộ các span của một trace trong 10-30 giây.
+- Khi trace kết thúc, bộ phân tích duyệt qua một lần duy nhất theo thang ưu tiên trên. Một trace chỉ phát thải đúng một bản ghi (single record) với danh sách các cờ thuộc tính đa chiều `tags = ['is_error', 'is_slow', 'is_expensive']`.
+3. **Bảo toàn Khả năng Chẩn đoán (Preserving Diagnosis)**:
+- Việc gắn đa cờ (multi-tagging) trên một bản ghi duy nhất cho phép kỹ sư truy vấn độc lập: `sample_reason: HIGH_COST AND is_slow: true` mà không bị lệch thống kê tổng lượng request.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nếu áp dụng các bộ lọc lấy mẫu độc lập song song (ví dụ: filter Error lấy 100%, filter Slow lấy 100%), những sự kiện vừa chậm vừa lỗi sẽ bị lưu hai lần, làm sai lệch hoàn toàn số liệu thống kê tổng lượng lưu lượng (double-counting error metrics) và làm đội chi phí lưu trữ. Áp dụng Tail-sampling theo thang thứ bậc với bộ đệm OpenTelemetry Collector bảo đảm mọi sự kiện dị biệt hiếm gặp đều được giữ lại 100% để chẩn đoán nhưng chỉ được ghi nhận một lần duy nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Collector Contrib: Tail Sampling Processor (https://github.com/open-telemetry/opentelemetry-collector-contrib/tree/main/processor/tailsamplingprocessor)</t>
         </is>
       </c>
     </row>
@@ -1264,10 +1353,28 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Debug khác accountability purpose, Actor/action/target/time.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Debug khác accountability purpose, Actor/action/target/time.</t>
+- 1.0đ: Phân định rạch ròi mục đích và vòng đời lưu trữ của Application Logs (ngắn hạn, có thể xóa) vs Audit Logs (dài hạn, WORM bất biến).
+- 1.0đ: Giải quyết xung đột pháp lý GDPR (Audit log được miễn trừ xóa theo quy định nghĩa vụ pháp lý).
+- 1.0đ: Thiết kế schema Audit Log chỉ ghi metadata hành động (ai, làm gì, lúc nào), tuyệt đối không chứa raw PII payload.
+- 1.0đ: Xử lý đúng kịch bản người dùng yêu cầu xóa trace: xóa application log nhưng lưu vết hành động xóa trong audit log.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Phân tách Rạch ròi giữa Application Logs và Audit Logs (Application/Audit Contracts):
+1. **Phân định Bản chất &amp; Hợp đồng Lưu trữ**:
+- **Application / Diagnostic Telemetry (Traces, Debug Logs, Metrics)**:
+  + Mục đích: Phục vụ kỹ sư gỡ lỗi kỹ thuật, đo độ trễ và tối ưu hiệu năng.
+  + Chính sách dữ liệu: Vòng đời ngắn (retention 14-30 ngày). Phải tuân thủ quyền được quên (Right to be Forgotten - GDPR Article 17). Khi có yêu cầu hợp lệ từ người dùng, toàn bộ trace ID liên quan sẽ bị xóa hoặc làm rỗng (hard delete / purge) khỏi Elasticsearch/Tempo.
+- **Audit / Compliance Logs (Nhật ký Kiểm toán Tuân thủ)**:
+  + Mục đích: Chứng minh tính hợp pháp, phòng chống gian lận và trách nhiệm giải trình trước pháp luật (Ai đã làm gì, với dữ liệu nào, vào lúc nào).
+  + Chính sách dữ liệu: Lưu trữ bất biến (Write-Once-Read-Many - WORM, S3 Object Lock), lưu tối thiểu 1 đến 5 năm theo quy định pháp lý, **MIỄN TRỪ XÓA** theo yêu cầu người dùng cá nhân (dựa trên cơ sở pháp lý Legal Obligation - GDPR Article 17(3)(b)).
+2. **Cấu trúc Dữ liệu Audit Log Chuẩn hóa (Zero PII Content)**:
+- Để giải quyết mâu thuẫn giữa việc lưu audit log lâu dài và bảo vệ PII, bản thân Audit Log **tuyệt đối không chứa raw data được export**:
+  `{ timestamp: '...', actor_id: 'user_123', action: 'EXPORT_PII_REPORT', resource_id: 'report_456', client_ip: '...', record_count: 50, justification: 'Legal audit' }`.
+3. **Kịch bản Xử lý Thực tế**:
+- Khi người dùng đọc export rồi yêu cầu xóa dữ liệu: Hệ thống thực hiện xóa bỏ toàn bộ application traces và nội dung export cá nhân; đồng thời ghi nhận thêm một dòng Audit Log: `{ actor_id: 'user_123', action: 'REQUEST_DATA_DELETION', status: 'SUCCESS' }`. Tính toàn vẹn của chuỗi kiểm toán được giữ nguyên vẹn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự nhầm lẫn giữa Application Logs và Audit Logs là sai lầm pháp lý phổ biến. Nếu lưu chung một nơi, khi thực hiện quyền xóa dữ liệu người dùng (GDPR Right to be Forgotten), doanh nghiệp sẽ vi phạm quy định lưu trữ kiểm toán tài chính (SOX, ISO 27001). Ngược lại, nếu từ chối xóa vì lý do lưu log, doanh nghiệp sẽ vi phạm luật bảo vệ dữ liệu cá nhân. Giải pháp là tách rời vật lý hai hệ thống: Trace/App log lưu tạm thời và có thể xóa; Audit log lưu siêu dữ liệu hành động trên kho bất biến (WORM storage) và không chứa nội dung nhạy cảm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+GDPR Article 17 (Right to erasure) &amp; NIST SP 800-92: Guide to Computer Security Log Management</t>
         </is>
       </c>
     </row>
@@ -1346,10 +1453,31 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Trace identity, Root/child span.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Trace identity, Root/child span.</t>
+- 1.0đ: Dựng đồ thị trace trực quan thể hiện rõ luồng Fan-out hai tool song song và hội tụ tại bước Join Synthesis.
+- 1.0đ: Xác định chuẩn xác quan hệ phân cấp context (parent-child span relationship, span_id, trace_id).
+- 1.0đ: Thiết lập hợp đồng trạng thái (Status Contract) xử lý chuẩn xác trường hợp một tool bị lỗi (error propagation).
+- 1.0đ: Định nghĩa cơ chế ghi nhận suy thoái cục bộ (graceful degradation metadata) tại tầng synthesis và root span.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Dựng Trace Graph (Biểu đồ Cây Span Phân tán):
+```text
+[Root Span: User Agent Request] (duration: 850ms, status: OK)
+ ├── [Span 1: Prompt Planning &amp; Routing] (duration: 120ms, status: OK)
+ ├── [Span 2: Parallel Tool Fan-out Dispatcher] (duration: 450ms, status: OK)
+ │    ├── [Span 2.1: Tool A - Weather API] (duration: 380ms, status: OK, parent: Span 2)
+ │    └── [Span 2.2: Tool B - Stock API]   (duration: 450ms, status: ERROR, parent: Span 2)
+ └── [Span 3: Join &amp; Response Synthesis]   (duration: 280ms, status: OK, parent: Root Span)
+```
+2. Hợp đồng Ngữ cảnh &amp; Trạng thái (Context &amp; Status Contract):
+- **Quan hệ Cha-Con (Parent-Child Hierarchy)**: Cả `Span 2.1` và `Span 2.2` cùng có `parent_span_id` trỏ về `Span 2` (Fan-out dispatcher). Span 3 bắt đầu sau khi Span 2 hoàn thành (hoặc sau khi barrier join kết thúc).
+- **Quy tắc Trạng thái khi có Tool Lỗi (Partial Failure Status Contract)**:
+  + Nếu Tool B gặp lỗi (`Span 2.2` có `status = ERROR`), Span 2.2 phải ghi nhận error event và exception stack.
+  + **Dispatcher Span 2**: Nếu ứng dụng có cơ chế chịu lỗi (graceful degradation), Span 2 có thể đánh dấu `status = OK` nhưng bổ sung thuộc tính `tool_execution_mode = 'partial_success'` và `failed_tools = ['Stock API']`.
+  + **Synthesis Span 3**: Tiếp nhận kết quả từ Tool A kèm thông báo lỗi của Tool B để tổng hợp câu trả lời cứu vãn cho người dùng.
+  + **Root Span**: Trả về `status = OK` kèm mã HTTP 200 vì nghiệp vụ được hoàn thành có suy thoái, nhưng ghi nhận metric `agent_partial_degradation_total` để cảnh báo SRE.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Mô hình Ngữ cảnh Trace Span (Trace Context Model): Trong các luồng tính toán song song (fan-out), các sub-span công cụ phải kế thừa chính xác span cha của bộ điều phối. Quan trọng hơn, hệ thống phải có hợp đồng trạng thái rõ ràng đối với lỗi cục bộ (partial failure): một tool con thất bại không nhất thiết phải làm sập toàn bộ trace nếu tầng tổng hợp (synthesis) có logic fallback. Trace phải phản ánh chân thực: span con lỗi (ERROR), nhưng span cha hoàn thành nhiệm vụ cứu vãn (OK with partial tag).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Tracing Specification: Span Relationships (https://opentelemetry.io/docs/concepts/signals/traces/) &amp; W3C Trace Context</t>
         </is>
       </c>
     </row>
@@ -1428,10 +1556,28 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Root invocation, Model generation span.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Root invocation, Model generation span.</t>
+- 1.0đ: Thiết kế span bao bọc phân cấp rõ ràng (Root Session -&gt; Loop Step -&gt; Model/Tool Spans).
+- 1.0đ: Thể hiện chuẩn xác 3 model attempts thành các span con có thuộc tính đo lường token và finish_reason.
+- 1.0đ: Đóng gói 2 tool retries trong cấu trúc span logical call phân định rõ nỗ lực lỗi và nỗ lực thành công.
+- 1.0đ: Áp dụng nguyên tắc chống vỡ vụn trace (dùng Span Events/Attributes cho trivial work thay vì spam spans).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Ranh giới Span (Span Boundary Design) cho Agent Loop có 3 Model Attempts và 2 Tool Retries:
+1. **Ranh giới Span theo Phân cấp Nghiệp vụ (Coarse-grained vs Fine-grained)**:
+- **Root Span: `agent.session.execution`**: Bao trùm toàn bộ phiên làm việc của Agent từ lúc nhận prompt đến khi xuất kết quả.
+- **Loop Iteration Spans: `agent.loop.step[i]`** ($i=1,2,3$): Mỗi vòng lặp suy luận được đóng gói trong một span trung gian để đo lường chi phí thời gian của từng turn.
+- **Model Execution Spans (Attempts)**:
+  + Đặt ranh giới: Mỗi lần gọi LLM là một span riêng biệt: `llm.call.attempt{attempt=1}`, `llm.call.attempt{attempt=2}`, `llm.call.attempt{attempt=3}`.
+  + Thuộc tính span: Ghi nhận `attempt_index`, `model`, `input_tokens`, `output_tokens`, `finish_reason`.
+- **Tool Execution Spans (Retries)**:
+  + Span bao ngoài: `tool.logical_call{tool_name='database_query'}`.
+  + Span bên trong: `tool.attempt{attempt=1, status=ERROR}` và `tool.attempt{attempt=2, status=OK}` nằm lồng bên trong span logical call.
+2. **Nguyên tắc Chống vỡ vụn Trace (Preventing Trace Fragmentation)**:
+- **Không tạo span cho các hàm nội bộ nhỏ (Trivial Operations)**: Các thao tác như format string, parse JSON, regex matching, nối mảng được ghi nhận dưới dạng **Span Events** hoặc thuộc tính (Attributes) bên trong span cha, tuyệt đối không tạo span độc lập.
+- **Lợi ích**: Giữ cho biểu đồ trace gọn gàng, thể hiện rõ chuỗi 3 lượt gọi model và 2 lần thử tool mà không sinh ra hàng trăm span rác làm quá tải collector.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Ranh giới Span cho AI Agent: Một sai lầm phổ biến là instrument thái quá (over-instrumentation), biến mọi hàm Python đơn giản thành một span, dẫn đến biểu đồ trace khổng lồ, nghẽn mạng và khó quan sát. Ranh giới chuẩn mực là: chỉ tạo Span cho các ranh giới mạng (network boundaries) và các bước suy luận có trạng thái (model attempts, tool execution, loop steps); các tác vụ nhỏ tính toán bằng micro-giây chỉ nên là Span Event.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Semantic Conventions for Generative AI (https://opentelemetry.io/docs/specs/semconv/gen-ai/) &amp; Honeycomb: Distributed Tracing Anti-patterns</t>
         </is>
       </c>
     </row>
